--- a/reports/Тест-план.xlsx
+++ b/reports/Тест-план.xlsx
@@ -296,6 +296,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -313,9 +316,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -631,38 +631,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="16">
         <v>46102</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="16"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="16"/>
+      <c r="C3" s="17"/>
     </row>
     <row r="4" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="17"/>
+      <c r="C4" s="18"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -961,22 +961,22 @@
       <c r="B37" s="3"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B38" s="14"/>
+      <c r="B38" s="15"/>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B39" s="13"/>
+      <c r="B39" s="14"/>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B40" s="13"/>
+      <c r="B40" s="14"/>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="10"/>
@@ -1034,6 +1034,7 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1"/>
+    <hyperlink ref="B33" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
